--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484876_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484876_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.2236</v>
+        <v>-1.0648</v>
       </c>
       <c r="E3" t="n">
         <v>-1.0229</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2006</v>
+        <v>-0.0419</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5644</v>
@@ -688,13 +688,13 @@
         <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7347</v>
+        <v>-1.576</v>
       </c>
       <c r="T3" t="n">
         <v>-0.4115</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3232</v>
+        <v>-1.1645</v>
       </c>
       <c r="V3" t="n">
         <v>0.3208</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.731</v>
+        <v>-1.3716</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2105</v>
+        <v>-1.9569</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4795</v>
+        <v>0.5853</v>
       </c>
       <c r="G4" t="n">
         <v>0.2864</v>
@@ -766,13 +766,13 @@
         <v>0.7548</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8853</v>
+        <v>-0.5258</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4703</v>
+        <v>-0.2166</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.415</v>
+        <v>-0.3092</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.1635</v>
+        <v>-4.6481</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1558</v>
+        <v>-1.0583</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.0077</v>
+        <v>-3.5897</v>
       </c>
       <c r="G5" t="n">
         <v>0.6325</v>
@@ -844,13 +844,13 @@
         <v>1.887</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.3055</v>
+        <v>-2.79</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0458</v>
+        <v>-0.9484</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2596</v>
+        <v>-1.8416</v>
       </c>
       <c r="V5" t="n">
         <v>-1.547</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.6295</v>
+        <v>-5.3733</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.9746</v>
+        <v>-2.8772</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6549</v>
+        <v>-2.4961</v>
       </c>
       <c r="G6" t="n">
         <v>-1.6517</v>
@@ -922,13 +922,13 @@
         <v>1.1322</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4872</v>
+        <v>-1.2311</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1345</v>
+        <v>-0.9758</v>
       </c>
       <c r="V6" t="n">
         <v>-1.547</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. ALFEREZ CANSECO</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.7884</v>
+        <v>-6.3949</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.2837</v>
+        <v>-4.9351</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5046</v>
+        <v>-1.4598</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.1651</v>
+        <v>-2.6536</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7319</v>
+        <v>-1.9674</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.4332</v>
+        <v>-0.6862</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.3437</v>
+        <v>-1.4764</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5596</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.7842</v>
+        <v>-0.5999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8213</v>
+        <v>-1.1772</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1723</v>
+        <v>-1.0909</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.649</v>
+        <v>-0.0863</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1887</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0757</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>1.887</v>
+        <v>1.5096</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1328</v>
+        <v>-2.4204</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1357</v>
+        <v>-0.6282</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.2685</v>
+        <v>-1.7923</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>D. ALFEREZ CANSECO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.7015</v>
+        <v>-6.5115</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.1887</v>
+        <v>-4.8482</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5127</v>
+        <v>-1.6634</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.6536</v>
+        <v>-4.1651</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.9674</v>
+        <v>-1.7319</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6862</v>
+        <v>-2.4332</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.4764</v>
+        <v>-2.3437</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.5596</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5999</v>
+        <v>-1.7842</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1772</v>
+        <v>-1.8213</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0909</v>
+        <v>-1.1723</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0863</v>
+        <v>-0.649</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3209</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8305</v>
+        <v>-2.0757</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.727</v>
+        <v>-1.856</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8818</v>
+        <v>-0.4288</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.8452</v>
+        <v>-1.4272</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.0547</v>
+        <v>-6.5894</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.3775</v>
+        <v>-4.1238</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6772</v>
+        <v>-2.4656</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5474</v>
@@ -1156,13 +1156,13 @@
         <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.111</v>
+        <v>-1.6457</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7519</v>
+        <v>-0.4982</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3591</v>
+        <v>-1.1474</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8868</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.138</v>
+        <v>-6.6223</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2558</v>
+        <v>-2.846</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.8821</v>
+        <v>-3.7763</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6574</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1597</v>
+        <v>-1.644</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.4596</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2903</v>
+        <v>-1.1844</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1886</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>J. NUNEZ NIEVAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.234</v>
+        <v>-7.3954</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0737</v>
+        <v>-3.7987</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1603</v>
+        <v>-3.5967</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.3303</v>
+        <v>-2.8778</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.7933</v>
+        <v>-3.1421</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.537</v>
+        <v>0.2643</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7721</v>
+        <v>0.4114</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9057</v>
+        <v>-0.9133</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8664</v>
+        <v>1.3247</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5582</v>
+        <v>-3.2891</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8876</v>
+        <v>-2.2288</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6706</v>
+        <v>-1.0603</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.7175</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.7932</v>
+        <v>-3.9627</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4878</v>
+        <v>-2.7438</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1118</v>
+        <v>-0.851</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.376</v>
+        <v>-1.8928</v>
       </c>
       <c r="V11" t="n">
-        <v>5.3016</v>
+        <v>0.3018</v>
       </c>
       <c r="W11" t="n">
-        <v>5.6034</v>
+        <v>0.6036</v>
       </c>
       <c r="X11" t="n">
         <v>-0.3018</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. NUNEZ NIEVAS</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8607</v>
+        <v>-7.9656</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0523</v>
+        <v>-5.5407</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.8084</v>
+        <v>-2.4249</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8778</v>
+        <v>-6.3303</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.1421</v>
+        <v>-3.7933</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2643</v>
+        <v>-2.537</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4114</v>
+        <v>-3.7721</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9133</v>
+        <v>-1.9057</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3247</v>
+        <v>-1.8664</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2891</v>
+        <v>-2.5582</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2288</v>
+        <v>-1.8876</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0603</v>
+        <v>-0.6706</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0757</v>
+        <v>-4.7175</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9627</v>
+        <v>-6.7932</v>
       </c>
       <c r="R12" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.2091</v>
+        <v>-2.2194</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1046</v>
+        <v>-0.5788</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1044</v>
+        <v>-1.6406</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3018</v>
+        <v>5.3016</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6036</v>
+        <v>5.6034</v>
       </c>
       <c r="X12" t="n">
         <v>-0.3018</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-53.90790000000001</v>
+        <v>-53.3199</v>
       </c>
       <c r="E13" t="n">
-        <v>-32.9785</v>
+        <v>-32.3908</v>
       </c>
       <c r="F13" t="n">
-        <v>-20.929</v>
+        <v>-20.9291</v>
       </c>
       <c r="G13" t="n">
         <v>-19.9118</v>
@@ -1441,13 +1441,13 @@
         <v>0.3260000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-5.299100000000001</v>
+        <v>-5.299099999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.838199999999999</v>
+        <v>-5.8382</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5391999999999999</v>
+        <v>0.5391999999999997</v>
       </c>
       <c r="M13" t="n">
         <v>-14.6125</v>
@@ -1468,10 +1468,10 @@
         <v>15.096</v>
       </c>
       <c r="S13" t="n">
-        <v>-19.2401</v>
+        <v>-18.6522</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.8642</v>
+        <v>-5.2764</v>
       </c>
       <c r="U13" t="n">
         <v>-13.3758</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.7516</v>
+        <v>9.5824</v>
       </c>
       <c r="E14" t="n">
-        <v>5.015</v>
+        <v>3.8458</v>
       </c>
       <c r="F14" t="n">
         <v>5.7367</v>
@@ -1546,10 +1546,10 @@
         <v>3.9627</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2378</v>
+        <v>3.0685</v>
       </c>
       <c r="T14" t="n">
-        <v>3.557</v>
+        <v>2.3878</v>
       </c>
       <c r="U14" t="n">
         <v>0.6808</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.534</v>
+        <v>8.721500000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0338</v>
+        <v>3.962</v>
       </c>
       <c r="F15" t="n">
-        <v>5.5002</v>
+        <v>4.7595</v>
       </c>
       <c r="G15" t="n">
         <v>3.9155</v>
@@ -1624,13 +1624,13 @@
         <v>2.8305</v>
       </c>
       <c r="S15" t="n">
-        <v>5.0714</v>
+        <v>3.2589</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1208</v>
+        <v>2.049</v>
       </c>
       <c r="U15" t="n">
-        <v>1.9506</v>
+        <v>1.2099</v>
       </c>
       <c r="V15" t="n">
         <v>0.6036</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5985</v>
+        <v>7.7476</v>
       </c>
       <c r="E16" t="n">
-        <v>5.6782</v>
+        <v>5.4833</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9203</v>
+        <v>2.2642</v>
       </c>
       <c r="G16" t="n">
         <v>3.9938</v>
@@ -1702,13 +1702,13 @@
         <v>3.2079</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6612</v>
+        <v>1.8102</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5031</v>
+        <v>1.3082</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1581</v>
+        <v>0.5021</v>
       </c>
       <c r="V16" t="n">
         <v>0.6226</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.0595</v>
+        <v>7.7235</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2463</v>
+        <v>2.8309</v>
       </c>
       <c r="F17" t="n">
-        <v>4.8132</v>
+        <v>4.8926</v>
       </c>
       <c r="G17" t="n">
         <v>0.965</v>
@@ -1780,13 +1780,13 @@
         <v>3.0192</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5284</v>
+        <v>2.1924</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9246</v>
+        <v>1.5092</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6038</v>
+        <v>0.6831</v>
       </c>
       <c r="V17" t="n">
         <v>2.4904</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>7.0423</v>
+        <v>7.0881</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9842</v>
+        <v>2.3739</v>
       </c>
       <c r="F18" t="n">
-        <v>5.0581</v>
+        <v>4.7142</v>
       </c>
       <c r="G18" t="n">
         <v>4.645</v>
@@ -1858,13 +1858,13 @@
         <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8312</v>
+        <v>1.877</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6278</v>
+        <v>1.0175</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2034</v>
+        <v>0.8595</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4178</v>
+        <v>4.6102</v>
       </c>
       <c r="E19" t="n">
-        <v>0.72</v>
+        <v>2.3424</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6978</v>
+        <v>2.2678</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6734</v>
+        <v>4.2682</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2731</v>
+        <v>1.85</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4003</v>
+        <v>2.4182</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6253</v>
+        <v>4.3771</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0994</v>
+        <v>1.7859</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7248</v>
+        <v>2.5912</v>
       </c>
       <c r="M19" t="n">
-        <v>0.048</v>
+        <v>-0.1089</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3725</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3245</v>
+        <v>-0.173</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7548</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>2.4531</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4426</v>
+        <v>1.361</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1328</v>
+        <v>0.8148</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3098</v>
+        <v>0.5461</v>
       </c>
       <c r="V19" t="n">
-        <v>1.547</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8488</v>
+        <v>-0.019</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3018</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1775</v>
+        <v>4.504</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8809</v>
+        <v>1.5969</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2966</v>
+        <v>2.9071</v>
       </c>
       <c r="G20" t="n">
-        <v>4.2682</v>
+        <v>0.6734</v>
       </c>
       <c r="H20" t="n">
-        <v>1.85</v>
+        <v>0.2731</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4182</v>
+        <v>0.4003</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3771</v>
+        <v>0.6253</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7859</v>
+        <v>-0.0994</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5912</v>
+        <v>0.7248</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1089</v>
+        <v>0.048</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.3725</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.173</v>
+        <v>-0.3245</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3774</v>
+        <v>0.7548</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8305</v>
+        <v>-1.887</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4531</v>
+        <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0717</v>
+        <v>1.5288</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6467000000000001</v>
+        <v>1.0097</v>
       </c>
       <c r="U20" t="n">
-        <v>0.575</v>
+        <v>0.5191</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.547</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.019</v>
+        <v>1.8488</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6226</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. GONZALEZ JURADO</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.7861</v>
+        <v>1.8999</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1579</v>
+        <v>-2.1248</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6282</v>
+        <v>4.0247</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9094</v>
+        <v>-2.1361</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2797</v>
+        <v>0.0117</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1891</v>
+        <v>-2.1478</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9903</v>
+        <v>-2.5684</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4846</v>
+        <v>-0.0525</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.4749</v>
+        <v>-2.516</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0809</v>
+        <v>0.4324</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7951</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7143</v>
+        <v>0.3682</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4531</v>
+        <v>3.0192</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4877</v>
+        <v>1.9603</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7898</v>
+        <v>1.3871</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3021</v>
+        <v>0.5732</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ó. GONZÁLEZ JURADO</t>
+          <t>O. GONZALEZ JURADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2509</v>
+        <v>1.4977</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2509</v>
+        <v>-0.4985</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.9962</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2509</v>
+        <v>-0.9094</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6339</v>
+        <v>2.2797</v>
       </c>
       <c r="I22" t="n">
-        <v>0.617</v>
+        <v>-3.1891</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2509</v>
+        <v>-0.9903</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6339</v>
+        <v>1.4846</v>
       </c>
       <c r="L22" t="n">
-        <v>0.617</v>
+        <v>-2.4749</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>0.0809</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.7951</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.7143</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.1993</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.1335</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.0659</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>Ó. GONZÁLEZ JURADO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6791</v>
+        <v>1.2509</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0017</v>
+        <v>1.2509</v>
       </c>
       <c r="F23" t="n">
-        <v>3.6808</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1361</v>
+        <v>1.2509</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0117</v>
+        <v>0.6339</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1478</v>
+        <v>0.617</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5684</v>
+        <v>1.2509</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0525</v>
+        <v>0.6339</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.516</v>
+        <v>0.617</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4324</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.06419999999999999</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3682</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.0192</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5102</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2293</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5044</v>
+        <v>1.166</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9786</v>
+        <v>-0.394</v>
       </c>
       <c r="F24" t="n">
-        <v>1.483</v>
+        <v>1.56</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0544</v>
@@ -2326,13 +2326,13 @@
         <v>1.3209</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1775</v>
+        <v>0.4841</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5291</v>
+        <v>0.0555</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3516</v>
+        <v>0.4286</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5846</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8939</v>
+        <v>-1.2344</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3009</v>
+        <v>-0.3811</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1948</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>0.107</v>
@@ -2404,13 +2404,13 @@
         <v>0.9435</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4896</v>
+        <v>1.1491</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3855</v>
+        <v>0.7034</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1041</v>
+        <v>0.4456</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4904</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>53.90779999999999</v>
+        <v>54.5574</v>
       </c>
       <c r="E26" t="n">
-        <v>20.2878</v>
+        <v>20.2877</v>
       </c>
       <c r="F26" t="n">
-        <v>33.62009999999999</v>
+        <v>34.2697</v>
       </c>
       <c r="G26" t="n">
         <v>19.9118</v>
@@ -2452,7 +2452,7 @@
         <v>20.2377</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3260000000000002</v>
+        <v>-0.3259999999999997</v>
       </c>
       <c r="J26" t="n">
         <v>14.6125</v>
@@ -2464,7 +2464,7 @@
         <v>0.2130000000000006</v>
       </c>
       <c r="M26" t="n">
-        <v>5.299200000000001</v>
+        <v>5.2992</v>
       </c>
       <c r="N26" t="n">
         <v>5.838299999999999</v>
@@ -2482,13 +2482,13 @@
         <v>28.305</v>
       </c>
       <c r="S26" t="n">
-        <v>19.2402</v>
+        <v>19.8896</v>
       </c>
       <c r="T26" t="n">
-        <v>13.3758</v>
+        <v>13.3757</v>
       </c>
       <c r="U26" t="n">
-        <v>5.864400000000001</v>
+        <v>6.5139</v>
       </c>
       <c r="V26" t="n">
         <v>1.547000000000001</v>
